--- a/시나리오 영역_시나리오그림포함_V1.5_20260830.xlsx
+++ b/시나리오 영역_시나리오그림포함_V1.5_20260830.xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.625" customWidth="1" style="71" min="2" max="9"/>
@@ -4851,7 +4851,7 @@
       <c r="M68" s="106" t="inlineStr">
         <is>
           <t>IDLE 복귀
-(2026-08-30) 완료 상태 9 신설 : 입고 완료(29) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 입고 완료(29) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -4904,7 +4904,7 @@
           <t>PollObservations()
 CompleteSC()
 GetJobCompleteReport()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.625" customWidth="1" style="71" min="2" max="9"/>
@@ -8631,7 +8631,7 @@
       <c r="M68" s="106" t="inlineStr">
         <is>
           <t>IDLE 복귀
-(2026-08-30) 완료 상태 9 신설 : 입고 완료(29) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 입고 완료(29) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -8684,7 +8684,7 @@
           <t>PollObservations()
 CompleteSC()
 GetJobCompleteReport()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.625" customWidth="1" style="71" min="2" max="9"/>
@@ -12411,7 +12411,7 @@
       <c r="M68" s="106" t="inlineStr">
         <is>
           <t>IDLE 복귀
-(2026-08-30) 완료 상태 9 신설 : 입고 완료(29) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 입고 완료(29) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -12464,7 +12464,7 @@
           <t>PollObservations()
 CompleteSC()
 GetJobCompleteReport()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="21" min="1" max="1"/>
@@ -15855,7 +15855,7 @@
           <t>29 피킹대 반출 완료 (작업자 회수)
 (2026-08-30) 출고대 신호 ON → 상위 도착보고 → 응답 수신 시 작업 삭제.
  지게차 반출은 신호 ON +OUT_REMOVE_MS 화물감지 OFF, +OUT_TRACK_CLEAR_MS 트래킹 제거.
-(2026-08-30) 완료 상태 9 신설 : 출고 완료(19) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 출고 완료(19) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -15908,7 +15908,7 @@
           <t>UpdateStationSignals()   (출고대=화물O+데이터O)
 ReportOutStationArrival()  (JOB_STATUS→22)
 GetLoadArrivalReport() → DeleteJobMst()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="21" min="1" max="1"/>
@@ -19299,7 +19299,7 @@
           <t>26 출고대 반출 완료 (작업자 회수)
 (2026-08-30) 출고대 신호 ON → 상위 도착보고 → 응답 수신 시 작업 삭제.
  지게차 반출은 신호 ON +OUT_REMOVE_MS 화물감지 OFF, +OUT_TRACK_CLEAR_MS 트래킹 제거.
-(2026-08-30) 완료 상태 9 신설 : 출고 완료(19) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 출고 완료(19) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -19352,7 +19352,7 @@
           <t>UpdateStationSignals()   (출고대=화물O+데이터O)
 ReportOutStationArrival()  (JOB_STATUS→22)
 GetLoadArrivalReport() → DeleteJobMst()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="21" min="1" max="1"/>
@@ -22743,7 +22743,7 @@
           <t>입출고대 반출 완료 (작업자 회수)
 (2026-08-30) 출고대 신호 ON → 상위 도착보고 → 응답 수신 시 작업 삭제.
  지게차 반출은 신호 ON +OUT_REMOVE_MS 화물감지 OFF, +OUT_TRACK_CLEAR_MS 트래킹 제거.
-(2026-08-30) 완료 상태 9 신설 : 출고 완료(19) → 9(완료) → 상위 응답 수신 → 작업 삭제.
+(2026-08-30) 완료 상태 09 신설 : 출고 완료(19) → 09(완료) → 상위 응답 수신 → 작업 삭제.
  송신 실패 시 원래 상태로 되돌려 다음 주기에 재보고한다.</t>
         </is>
       </c>
@@ -22796,7 +22796,7 @@
           <t>UpdateStationSignals()   (출고대=화물O+데이터O)
 ReportOutStationArrival()  (JOB_STATUS→22)
 GetLoadArrivalReport() → DeleteJobMst()
-UpdateJobStatusTo(9) → DeleteJobMst()</t>
+UpdateJobStatusTo(09) → DeleteJobMst()</t>
         </is>
       </c>
     </row>
